--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -427,13 +427,13 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mức dùng theo quy trình</t>
+          <t>Mức dùng ChatGPT khi viết content marketing</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Log quy trình</t>
+          <t>Log dùng ChatGPT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trưởng nhóm</t>
+          <t>Trưởng nhóm marketing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,17 +513,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thời gian / năng suất</t>
+          <t>Chất lượng content AI viết ra (có dài/thừa không)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Đo hiện trạng</t>
+          <t>Đo mẫu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,34 +533,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Log tác vụ</t>
+          <t>Quan sát/phản hồi người viết</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chủ quy trình</t>
+          <t>Phụ trách QA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Xem lại cách làm</t>
+          <t>Tăng kiểm soát</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chất lượng / tin cậy (vd: tỷ lệ câu trả lời có nguồn)</t>
+          <t>Thời gian viết 1 bài content</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Đo mẫu</t>
+          <t>Đo hiện trạng</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,24 +570,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kiểm tra mẫu</t>
+          <t>Log tác vụ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Phụ trách QA</t>
+          <t>Chủ quy trình content</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tăng kiểm soát</t>
+          <t>Xem lại cách làm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kết quả nghiệp vụ</t>
+          <t>Kết quả nghiệp vụ (hiệu quả content marketing)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rủi ro / bàn giao</t>
+          <t>Rủi ro khi AI viết sai/thiếu nguồn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,11 +652,7 @@
           <t>Phụ trách AI</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Bổ sung xử lý</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
